--- a/public/excel-templates/measurements.xlsx
+++ b/public/excel-templates/measurements.xlsx
@@ -418,172 +418,172 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SKELETON</v>
+        <v>SKELETAL_x000d_</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SNA</v>
+        <v>SNA_x000d_</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SNB</v>
+        <v>SNB_x000d_</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ANB</v>
+        <v>ANB_x000d_</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>A to N-Perp.</v>
+        <v>A to N-Perp._x000d_</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Pog to N-Perp.</v>
+        <v>Pog to N-Perp._x000d_</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Wits appraisal</v>
+        <v>Wits appraisal_x000d_</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>APDI</v>
+        <v>APDI_x000d_</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ODI</v>
+        <v>ODI_x000d_</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SN-GoMe</v>
+        <v>SN-GoMe_x000d_</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>FMA</v>
+        <v>FMA_x000d_</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Facial height ratio(PFH/AFH)</v>
+        <v>Facial height ratio(PFH/AFH)_x000d_</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>DENTAL</v>
+        <v>DENTAL_x000d_</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Interincisal angle</v>
+        <v>Interincisal angle_x000d_</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>U1 to SN</v>
+        <v>U1 to SN_x000d_</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>U1 to NA(deg)</v>
+        <v>U1 to NA(deg)_x000d_</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>U1 to NA(mm)</v>
+        <v>U1 to NA(mm)_x000d_</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>U1 to A-Pog(mm)</v>
+        <v>U1 to A-Pog(mm)_x000d_</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>IMPA</v>
+        <v>IMPA_x000d_</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>L1 to NB(deg)</v>
+        <v>L1 to NB(deg)_x000d_</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>L1 to NB(mm)</v>
+        <v>L1 to NB(mm)_x000d_</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>L1 to A-Pog(mm)</v>
+        <v>L1 to A-Pog(mm)_x000d_</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Occlusal plane to SN angle</v>
+        <v>Occlusal plane to SN angle_x000d_</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Overjet</v>
+        <v>Overjet_x000d_</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Overbite</v>
+        <v>Overbite_x000d_</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Growth prediction</v>
+        <v>Growth prediction_x000d_</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Saddle angle</v>
+        <v>Saddle angle_x000d_</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Articular angle</v>
+        <v>Articular angle_x000d_</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Gonial angle</v>
+        <v>Gonial angle_x000d_</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Bjork sum</v>
+        <v>Bjork sum_x000d_</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Combination factor</v>
+        <v>Combination factor_x000d_</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Body to Ant. cranial base ratio</v>
+        <v>Body to Ant. cranial base ratio_x000d_</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Soft tissue</v>
+        <v>Soft tissue_x000d_</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Upper lip to E-plane</v>
+        <v>Upper lip to E-plane_x000d_</v>
       </c>
     </row>
     <row r="36">
